--- a/enhancements/test-files/02_ARR_pc0101_2026_Jul.xlsx
+++ b/enhancements/test-files/02_ARR_pc0101_2026_Jul.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +487,41 @@
           <t>Transaction Effective Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -497,7 +539,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,16 +548,41 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17625.66</v>
+        <v>10522.39</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46207</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46082</v>
+        <v>46090</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46204</v>
+        <v>46207</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1262.69</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>593.46</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="P2" t="n">
+        <v>669.23</v>
       </c>
     </row>
     <row r="3">
@@ -529,7 +596,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -543,16 +610,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10054.14</v>
+        <v>6178.34</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46179</v>
+        <v>46090</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>46209</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>741.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>378.11</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="P3" t="n">
+        <v>363.29</v>
       </c>
     </row>
     <row r="4">
@@ -571,7 +663,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -580,16 +672,41 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11262.88</v>
+        <v>10813.95</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46035</v>
+        <v>46041</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46210</v>
+        <v>46211</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1297.67</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>869.4400000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="P4" t="n">
+        <v>428.23</v>
       </c>
     </row>
     <row r="5">
@@ -603,12 +720,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -617,16 +734,41 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2161.22</v>
+        <v>7877.29</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46089</v>
+        <v>46159</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>46216</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>945.27</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>661.6900000000001</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>283.58</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +787,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,16 +796,41 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3408.09</v>
+        <v>23991.94</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45936</v>
+        <v>46067</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46214</v>
+        <v>46218</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2879.03</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1900.16</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="P6" t="n">
+        <v>978.87</v>
       </c>
     </row>
   </sheetData>
